--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/121.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/121.xlsx
@@ -426,13 +426,13 @@
         <v>-16.7943383919267</v>
       </c>
       <c r="E2">
-        <v>-27.20663100160417</v>
+        <v>-11.82867663834657</v>
       </c>
       <c r="F2">
-        <v>-5.20373541713957</v>
+        <v>-1.132114966040342</v>
       </c>
       <c r="G2">
-        <v>-17.18234477017783</v>
+        <v>-11.4083580692292</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.8277665701532</v>
       </c>
       <c r="E3">
-        <v>-28.38564047928517</v>
+        <v>-11.92124756556567</v>
       </c>
       <c r="F3">
-        <v>-5.709268990617844</v>
+        <v>-0.9303735403951473</v>
       </c>
       <c r="G3">
-        <v>-16.32094656217984</v>
+        <v>-11.45781209864637</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.82552075551564</v>
       </c>
       <c r="E4">
-        <v>-27.97573928758122</v>
+        <v>-12.82048426877225</v>
       </c>
       <c r="F4">
-        <v>-5.321487015080117</v>
+        <v>-0.9414703501230495</v>
       </c>
       <c r="G4">
-        <v>-15.87658216830481</v>
+        <v>-11.34292367216984</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.75847111307137</v>
       </c>
       <c r="E5">
-        <v>-28.84277406678073</v>
+        <v>-13.47097268610087</v>
       </c>
       <c r="F5">
-        <v>-5.087964445659116</v>
+        <v>-1.097241526749885</v>
       </c>
       <c r="G5">
-        <v>-16.43110431945728</v>
+        <v>-11.43912047274629</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.63346355164789</v>
       </c>
       <c r="E6">
-        <v>-30.35099406994126</v>
+        <v>-14.79301460859764</v>
       </c>
       <c r="F6">
-        <v>-5.168932389078352</v>
+        <v>-0.8094020783599187</v>
       </c>
       <c r="G6">
-        <v>-15.69521504693247</v>
+        <v>-11.67355619942219</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.44365353024732</v>
       </c>
       <c r="E7">
-        <v>-28.55742560610273</v>
+        <v>-15.41754960835741</v>
       </c>
       <c r="F7">
-        <v>-4.739457853790323</v>
+        <v>-0.7045398772069321</v>
       </c>
       <c r="G7">
-        <v>-16.40224514874711</v>
+        <v>-11.30903751274948</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.20148880265734</v>
       </c>
       <c r="E8">
-        <v>-30.67778119661274</v>
+        <v>-15.09255251576693</v>
       </c>
       <c r="F8">
-        <v>-5.146114180600836</v>
+        <v>-0.2374334391771245</v>
       </c>
       <c r="G8">
-        <v>-15.77381803970941</v>
+        <v>-10.66005731691824</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.90713295434003</v>
       </c>
       <c r="E9">
-        <v>-30.54406440479856</v>
+        <v>-15.97987780889389</v>
       </c>
       <c r="F9">
-        <v>-4.332439530424785</v>
+        <v>-0.3652588131031161</v>
       </c>
       <c r="G9">
-        <v>-16.17777724492008</v>
+        <v>-9.999279166279766</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.57671309346359</v>
       </c>
       <c r="E10">
-        <v>-31.78076614099276</v>
+        <v>-16.72986470993143</v>
       </c>
       <c r="F10">
-        <v>-5.196845057083084</v>
+        <v>-0.1315266667292077</v>
       </c>
       <c r="G10">
-        <v>-15.67766170567412</v>
+        <v>-10.0703344964438</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.21654473407423</v>
       </c>
       <c r="E11">
-        <v>-31.0891297824634</v>
+        <v>-17.34424095479067</v>
       </c>
       <c r="F11">
-        <v>-4.809940322624921</v>
+        <v>-0.1042700657074927</v>
       </c>
       <c r="G11">
-        <v>-15.17671725502048</v>
+        <v>-9.269692231197908</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.84795550706569</v>
       </c>
       <c r="E12">
-        <v>-31.47345134561773</v>
+        <v>-18.09265794194742</v>
       </c>
       <c r="F12">
-        <v>-4.809715006691359</v>
+        <v>0.6155596697728049</v>
       </c>
       <c r="G12">
-        <v>-15.29867818859434</v>
+        <v>-8.852051418957515</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.48519162774537</v>
       </c>
       <c r="E13">
-        <v>-30.93938159493538</v>
+        <v>-18.90066935840414</v>
       </c>
       <c r="F13">
-        <v>-4.282616544616006</v>
+        <v>0.5174884245879686</v>
       </c>
       <c r="G13">
-        <v>-14.50306160668634</v>
+        <v>-8.490899287435042</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.14972467831237</v>
       </c>
       <c r="E14">
-        <v>-33.08363891661978</v>
+        <v>-19.98110651850166</v>
       </c>
       <c r="F14">
-        <v>-4.587440009865571</v>
+        <v>0.4868661668086793</v>
       </c>
       <c r="G14">
-        <v>-14.87518408698067</v>
+        <v>-8.804417078520357</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.8521011420925</v>
       </c>
       <c r="E15">
-        <v>-34.87496672294857</v>
+        <v>-20.29610267822196</v>
       </c>
       <c r="F15">
-        <v>-3.75844056273773</v>
+        <v>0.6241465262702246</v>
       </c>
       <c r="G15">
-        <v>-14.88841795131303</v>
+        <v>-8.040573258286207</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.59666678594895</v>
       </c>
       <c r="E16">
-        <v>-34.24735834680843</v>
+        <v>-21.58528439271668</v>
       </c>
       <c r="F16">
-        <v>-3.401703312354719</v>
+        <v>1.299684285090235</v>
       </c>
       <c r="G16">
-        <v>-13.91583987953018</v>
+        <v>-7.246850771579059</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.3810788995543</v>
       </c>
       <c r="E17">
-        <v>-34.84890947509659</v>
+        <v>-22.52708735879143</v>
       </c>
       <c r="F17">
-        <v>-3.761425998857419</v>
+        <v>1.560401327977741</v>
       </c>
       <c r="G17">
-        <v>-15.00293695742991</v>
+        <v>-7.11037148733402</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.19336304725654</v>
       </c>
       <c r="E18">
-        <v>-35.49394680256137</v>
+        <v>-22.56566653878776</v>
       </c>
       <c r="F18">
-        <v>-3.908553161636042</v>
+        <v>1.772857685978147</v>
       </c>
       <c r="G18">
-        <v>-13.8965634468417</v>
+        <v>-7.604958774908294</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.0209958088983</v>
       </c>
       <c r="E19">
-        <v>-36.24064851344097</v>
+        <v>-24.21415917783871</v>
       </c>
       <c r="F19">
-        <v>-3.961040177012224</v>
+        <v>2.168974694322842</v>
       </c>
       <c r="G19">
-        <v>-13.6031640535755</v>
+        <v>-6.502678911838945</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.84460219338281</v>
       </c>
       <c r="E20">
-        <v>-36.19743642621179</v>
+        <v>-24.75865348894638</v>
       </c>
       <c r="F20">
-        <v>-2.814407391117926</v>
+        <v>2.554165536624612</v>
       </c>
       <c r="G20">
-        <v>-13.74077640097308</v>
+        <v>-6.443999816409083</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.65698705127347</v>
       </c>
       <c r="E21">
-        <v>-37.41799047677506</v>
+        <v>-25.20399403288509</v>
       </c>
       <c r="F21">
-        <v>-2.111563329232032</v>
+        <v>2.849697204716975</v>
       </c>
       <c r="G21">
-        <v>-13.40472918943875</v>
+        <v>-5.892566176107908</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.4484191150263</v>
       </c>
       <c r="E22">
-        <v>-37.09149615150197</v>
+        <v>-26.3948983078004</v>
       </c>
       <c r="F22">
-        <v>-2.740308270202705</v>
+        <v>3.285357159401708</v>
       </c>
       <c r="G22">
-        <v>-13.73042610404161</v>
+        <v>-6.836003116764743</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.22678037955055</v>
       </c>
       <c r="E23">
-        <v>-38.84230522814573</v>
+        <v>-25.90221530796997</v>
       </c>
       <c r="F23">
-        <v>-2.722781672694273</v>
+        <v>3.378434177515066</v>
       </c>
       <c r="G23">
-        <v>-13.12894057381191</v>
+        <v>-6.378971390133633</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.99300253632732</v>
       </c>
       <c r="E24">
-        <v>-37.3426657595823</v>
+        <v>-25.99316648277239</v>
       </c>
       <c r="F24">
-        <v>-2.459099902872148</v>
+        <v>3.09854871292678</v>
       </c>
       <c r="G24">
-        <v>-13.11788407046855</v>
+        <v>-6.831314219479103</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.7622563722618</v>
       </c>
       <c r="E25">
-        <v>-38.79700615222583</v>
+        <v>-25.35120460829364</v>
       </c>
       <c r="F25">
-        <v>-2.310148675072561</v>
+        <v>3.454296064263445</v>
       </c>
       <c r="G25">
-        <v>-13.75805039256018</v>
+        <v>-6.429598949244502</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.53946623301641</v>
       </c>
       <c r="E26">
-        <v>-37.99665741066342</v>
+        <v>-27.182297336452</v>
       </c>
       <c r="F26">
-        <v>-2.013236946887134</v>
+        <v>3.141607250524299</v>
       </c>
       <c r="G26">
-        <v>-14.07473501683452</v>
+        <v>-6.497843812856203</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.34163637510829</v>
       </c>
       <c r="E27">
-        <v>-38.80160791037374</v>
+        <v>-26.33904592190411</v>
       </c>
       <c r="F27">
-        <v>-2.468855585774918</v>
+        <v>3.346649720269649</v>
       </c>
       <c r="G27">
-        <v>-14.20909829258846</v>
+        <v>-6.54858363398449</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.17560758643515</v>
       </c>
       <c r="E28">
-        <v>-38.95987433432898</v>
+        <v>-25.84660380833051</v>
       </c>
       <c r="F28">
-        <v>-2.593651620108872</v>
+        <v>2.973955628606512</v>
       </c>
       <c r="G28">
-        <v>-13.19335547510845</v>
+        <v>-6.704223172783708</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.05848758468775</v>
       </c>
       <c r="E29">
-        <v>-38.11796440703901</v>
+        <v>-26.87142116236593</v>
       </c>
       <c r="F29">
-        <v>-2.390140801691298</v>
+        <v>3.094587460006593</v>
       </c>
       <c r="G29">
-        <v>-12.94552010181866</v>
+        <v>-7.823027743742509</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.99847805307172</v>
       </c>
       <c r="E30">
-        <v>-37.55511082526994</v>
+        <v>-26.82965646928345</v>
       </c>
       <c r="F30">
-        <v>-2.584724304608902</v>
+        <v>2.683316298395083</v>
       </c>
       <c r="G30">
-        <v>-14.18824627553924</v>
+        <v>-6.706390090794333</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.0060309877651</v>
       </c>
       <c r="E31">
-        <v>-37.54562489060402</v>
+        <v>-27.0022930044226</v>
       </c>
       <c r="F31">
-        <v>-2.566912748713907</v>
+        <v>2.775979132807041</v>
       </c>
       <c r="G31">
-        <v>-13.42877806323979</v>
+        <v>-7.199734663943237</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.08131055043796</v>
       </c>
       <c r="E32">
-        <v>-37.42424728963591</v>
+        <v>-25.20569684952827</v>
       </c>
       <c r="F32">
-        <v>-2.760796281176145</v>
+        <v>2.947651650098017</v>
       </c>
       <c r="G32">
-        <v>-13.62945033549112</v>
+        <v>-7.564299038646296</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.219137081231</v>
       </c>
       <c r="E33">
-        <v>-37.1656787355804</v>
+        <v>-25.51366577568696</v>
       </c>
       <c r="F33">
-        <v>-2.189955878395963</v>
+        <v>2.954111259105047</v>
       </c>
       <c r="G33">
-        <v>-14.01785602980023</v>
+        <v>-7.550992073465392</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.4117890179494</v>
       </c>
       <c r="E34">
-        <v>-36.74340928055111</v>
+        <v>-25.30293598627648</v>
       </c>
       <c r="F34">
-        <v>-1.598982834258143</v>
+        <v>3.211044319696564</v>
       </c>
       <c r="G34">
-        <v>-14.00001420126456</v>
+        <v>-7.603598576976324</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.64597149073257</v>
       </c>
       <c r="E35">
-        <v>-36.64742441362299</v>
+        <v>-24.4323689008452</v>
       </c>
       <c r="F35">
-        <v>-3.023033378247787</v>
+        <v>2.97726909821771</v>
       </c>
       <c r="G35">
-        <v>-14.12112403210172</v>
+        <v>-8.292563631592756</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.91361292953922</v>
       </c>
       <c r="E36">
-        <v>-35.53251767613506</v>
+        <v>-23.41158016179486</v>
       </c>
       <c r="F36">
-        <v>-2.635662272941849</v>
+        <v>3.036141169534671</v>
       </c>
       <c r="G36">
-        <v>-13.48768298807679</v>
+        <v>-8.074220534576474</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.19729979550725</v>
       </c>
       <c r="E37">
-        <v>-36.53304289713155</v>
+        <v>-23.79092202457073</v>
       </c>
       <c r="F37">
-        <v>-2.145253859871291</v>
+        <v>3.137331217991048</v>
       </c>
       <c r="G37">
-        <v>-14.33284889157953</v>
+        <v>-8.54821035269916</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.490262040678</v>
       </c>
       <c r="E38">
-        <v>-35.80182643467658</v>
+        <v>-23.32574159013331</v>
       </c>
       <c r="F38">
-        <v>-2.437958310017899</v>
+        <v>3.276904498423542</v>
       </c>
       <c r="G38">
-        <v>-14.60934501899056</v>
+        <v>-8.759845141488576</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.77642002503984</v>
       </c>
       <c r="E39">
-        <v>-34.6181030621419</v>
+        <v>-22.56560008740657</v>
       </c>
       <c r="F39">
-        <v>-2.574836911289087</v>
+        <v>3.078893211193154</v>
       </c>
       <c r="G39">
-        <v>-14.93133337090175</v>
+        <v>-8.534071865365986</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.05638735531309</v>
       </c>
       <c r="E40">
-        <v>-33.7831227679474</v>
+        <v>-22.21617380580344</v>
       </c>
       <c r="F40">
-        <v>-2.484824024198684</v>
+        <v>3.399246080143001</v>
       </c>
       <c r="G40">
-        <v>-14.46334434922173</v>
+        <v>-9.428883688013336</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.32222582643492</v>
       </c>
       <c r="E41">
-        <v>-34.27112509861476</v>
+        <v>-22.39629442774993</v>
       </c>
       <c r="F41">
-        <v>-2.798856449865171</v>
+        <v>3.728573481534778</v>
       </c>
       <c r="G41">
-        <v>-15.05588285773769</v>
+        <v>-9.348197321052684</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.58271740264159</v>
       </c>
       <c r="E42">
-        <v>-33.90381924225824</v>
+        <v>-21.10455848829043</v>
       </c>
       <c r="F42">
-        <v>-2.115382931326341</v>
+        <v>3.644558802808046</v>
       </c>
       <c r="G42">
-        <v>-13.70118706999344</v>
+        <v>-9.365002683985681</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.83570725047544</v>
       </c>
       <c r="E43">
-        <v>-34.27306672490911</v>
+        <v>-20.20909705417812</v>
       </c>
       <c r="F43">
-        <v>-2.530102586435705</v>
+        <v>3.413934690929441</v>
       </c>
       <c r="G43">
-        <v>-15.88194333232266</v>
+        <v>-9.502393118093018</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.0931675024114</v>
       </c>
       <c r="E44">
-        <v>-33.69153822841795</v>
+        <v>-19.67376888046435</v>
       </c>
       <c r="F44">
-        <v>-2.183548456535309</v>
+        <v>3.479393939833464</v>
       </c>
       <c r="G44">
-        <v>-15.48452665305733</v>
+        <v>-9.548671176715091</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.35587828596831</v>
       </c>
       <c r="E45">
-        <v>-32.32495934427938</v>
+        <v>-19.45978297337521</v>
       </c>
       <c r="F45">
-        <v>-2.832425210496218</v>
+        <v>3.333821622669896</v>
       </c>
       <c r="G45">
-        <v>-14.82480193786137</v>
+        <v>-9.688335569361287</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.63436295249734</v>
       </c>
       <c r="E46">
-        <v>-33.68469373615463</v>
+        <v>-19.18402220104057</v>
       </c>
       <c r="F46">
-        <v>-2.100009260697785</v>
+        <v>3.456042262748546</v>
       </c>
       <c r="G46">
-        <v>-15.17034703821817</v>
+        <v>-9.618845380579625</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.92600247609308</v>
       </c>
       <c r="E47">
-        <v>-31.63467900924757</v>
+        <v>-18.64585323078061</v>
       </c>
       <c r="F47">
-        <v>-2.59314797272797</v>
+        <v>3.324051857521278</v>
       </c>
       <c r="G47">
-        <v>-15.30930391908017</v>
+        <v>-9.35394487527002</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-15.23227352121924</v>
       </c>
       <c r="E48">
-        <v>-31.3842632090227</v>
+        <v>-17.70422469958151</v>
       </c>
       <c r="F48">
-        <v>-2.388506432805574</v>
+        <v>3.386192666609686</v>
       </c>
       <c r="G48">
-        <v>-13.68832654213762</v>
+        <v>-8.992608686253872</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.54480629193615</v>
       </c>
       <c r="E49">
-        <v>-29.9036059928194</v>
+        <v>-16.86770979380249</v>
       </c>
       <c r="F49">
-        <v>-2.796941264429898</v>
+        <v>3.137245067781156</v>
       </c>
       <c r="G49">
-        <v>-14.26025322210674</v>
+        <v>-9.015275170793918</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.85717759717715</v>
       </c>
       <c r="E50">
-        <v>-30.95214233673092</v>
+        <v>-17.61951164818898</v>
       </c>
       <c r="F50">
-        <v>-2.824082722382624</v>
+        <v>3.130048211785634</v>
       </c>
       <c r="G50">
-        <v>-14.018923824338</v>
+        <v>-9.587076535022662</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-16.1589518086067</v>
       </c>
       <c r="E51">
-        <v>-29.19190754698546</v>
+        <v>-16.11778934414615</v>
       </c>
       <c r="F51">
-        <v>-3.158448254318228</v>
+        <v>3.370306236558797</v>
       </c>
       <c r="G51">
-        <v>-15.01097805077054</v>
+        <v>-8.894520401221156</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-16.44012086124554</v>
       </c>
       <c r="E52">
-        <v>-30.80946291487776</v>
+        <v>-15.67342065165745</v>
       </c>
       <c r="F52">
-        <v>-2.780287766164017</v>
+        <v>3.341498931759042</v>
       </c>
       <c r="G52">
-        <v>-14.63739746962207</v>
+        <v>-9.201637951941358</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-16.69215749362552</v>
       </c>
       <c r="E53">
-        <v>-30.71555465361206</v>
+        <v>-15.97455339197546</v>
       </c>
       <c r="F53">
-        <v>-2.728819642693278</v>
+        <v>2.897884993272628</v>
       </c>
       <c r="G53">
-        <v>-14.17162627547221</v>
+        <v>-9.373565926244533</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-16.90455749788296</v>
       </c>
       <c r="E54">
-        <v>-31.16925976515898</v>
+        <v>-15.78792053467164</v>
       </c>
       <c r="F54">
-        <v>-3.087553258517035</v>
+        <v>3.027216339136909</v>
       </c>
       <c r="G54">
-        <v>-13.70922424721718</v>
+        <v>-9.186438196931896</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-17.07488507119155</v>
       </c>
       <c r="E55">
-        <v>-29.31377107367858</v>
+        <v>-15.91590174164624</v>
       </c>
       <c r="F55">
-        <v>-2.596823438894191</v>
+        <v>2.82061488193949</v>
       </c>
       <c r="G55">
-        <v>-14.33839411309105</v>
+        <v>-9.289894172843942</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-17.19563775896435</v>
       </c>
       <c r="E56">
-        <v>-28.02489669682189</v>
+        <v>-14.60560510077608</v>
       </c>
       <c r="F56">
-        <v>-2.86858758946543</v>
+        <v>2.996566745233328</v>
       </c>
       <c r="G56">
-        <v>-14.98682344181356</v>
+        <v>-9.45170029036737</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-17.26935152601344</v>
       </c>
       <c r="E57">
-        <v>-28.96205637263547</v>
+        <v>-14.43540234747328</v>
       </c>
       <c r="F57">
-        <v>-2.952047262032286</v>
+        <v>2.820298445591621</v>
       </c>
       <c r="G57">
-        <v>-14.69965720125865</v>
+        <v>-8.904835453100644</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-17.28979570538501</v>
       </c>
       <c r="E58">
-        <v>-28.98610138960057</v>
+        <v>-14.12531113032761</v>
       </c>
       <c r="F58">
-        <v>-2.904992680083663</v>
+        <v>2.817616191941356</v>
       </c>
       <c r="G58">
-        <v>-14.33476126199252</v>
+        <v>-9.548475370870758</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-17.26140500226476</v>
       </c>
       <c r="E59">
-        <v>-28.71954621016741</v>
+        <v>-14.03634519053846</v>
       </c>
       <c r="F59">
-        <v>-2.748297045435303</v>
+        <v>2.682797740400931</v>
       </c>
       <c r="G59">
-        <v>-14.54570289809299</v>
+        <v>-9.820674212684819</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-17.17858835084851</v>
       </c>
       <c r="E60">
-        <v>-27.03820997595972</v>
+        <v>-13.49346647863614</v>
       </c>
       <c r="F60">
-        <v>-2.996393082573755</v>
+        <v>3.09966700892056</v>
       </c>
       <c r="G60">
-        <v>-15.09190460623358</v>
+        <v>-9.522910959834576</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-17.04895258931848</v>
       </c>
       <c r="E61">
-        <v>-27.81275066234964</v>
+        <v>-13.95824405157505</v>
       </c>
       <c r="F61">
-        <v>-2.515241675229482</v>
+        <v>2.677691683730075</v>
       </c>
       <c r="G61">
-        <v>-16.04669828586175</v>
+        <v>-9.357195252285956</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.86941725193203</v>
       </c>
       <c r="E62">
-        <v>-28.51045070941325</v>
+        <v>-13.39782632824799</v>
       </c>
       <c r="F62">
-        <v>-2.751899615270078</v>
+        <v>2.95276267697329</v>
       </c>
       <c r="G62">
-        <v>-14.51583728534295</v>
+        <v>-9.889449057448518</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.6512320719905</v>
       </c>
       <c r="E63">
-        <v>-28.2526027375226</v>
+        <v>-12.66559440562409</v>
       </c>
       <c r="F63">
-        <v>-2.896810895246213</v>
+        <v>3.241480194810224</v>
       </c>
       <c r="G63">
-        <v>-14.53225103658728</v>
+        <v>-10.03134563672011</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.39217607256796</v>
       </c>
       <c r="E64">
-        <v>-28.99654463947685</v>
+        <v>-12.59257264411096</v>
       </c>
       <c r="F64">
-        <v>-2.925033372659592</v>
+        <v>2.65309248533654</v>
       </c>
       <c r="G64">
-        <v>-15.59156848666527</v>
+        <v>-9.942165212232277</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.10425083649232</v>
       </c>
       <c r="E65">
-        <v>-27.98071483474836</v>
+        <v>-12.99287161123191</v>
       </c>
       <c r="F65">
-        <v>-2.50252043702469</v>
+        <v>2.758745777359201</v>
       </c>
       <c r="G65">
-        <v>-15.65173701188436</v>
+        <v>-10.24964565645064</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.78618853273038</v>
       </c>
       <c r="E66">
-        <v>-27.60516900712339</v>
+        <v>-13.24939055549862</v>
       </c>
       <c r="F66">
-        <v>-2.884073089693365</v>
+        <v>2.432229854932525</v>
       </c>
       <c r="G66">
-        <v>-15.30743332058064</v>
+        <v>-10.40058063349668</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.45280347178856</v>
       </c>
       <c r="E67">
-        <v>-25.43510778347783</v>
+        <v>-12.40617236664133</v>
       </c>
       <c r="F67">
-        <v>-2.434017766282782</v>
+        <v>2.613879229222817</v>
       </c>
       <c r="G67">
-        <v>-15.06088504437427</v>
+        <v>-10.34255161347</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.10611053637955</v>
       </c>
       <c r="E68">
-        <v>-28.67818437858344</v>
+        <v>-13.00405620932967</v>
       </c>
       <c r="F68">
-        <v>-3.137572567400277</v>
+        <v>2.683508479632533</v>
       </c>
       <c r="G68">
-        <v>-15.69077939187217</v>
+        <v>-10.16478862500569</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.7624466460365</v>
       </c>
       <c r="E69">
-        <v>-27.78462926846923</v>
+        <v>-12.71784180409044</v>
       </c>
       <c r="F69">
-        <v>-3.765668068327155</v>
+        <v>2.777622613734196</v>
       </c>
       <c r="G69">
-        <v>-15.80888817180184</v>
+        <v>-10.31406186311948</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.42396086066668</v>
       </c>
       <c r="E70">
-        <v>-26.52603595538186</v>
+        <v>-12.98108895070337</v>
       </c>
       <c r="F70">
-        <v>-3.393783291616554</v>
+        <v>2.810150944907327</v>
       </c>
       <c r="G70">
-        <v>-15.06091637330936</v>
+        <v>-10.42546233482228</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.10513328593177</v>
       </c>
       <c r="E71">
-        <v>-27.11576704423957</v>
+        <v>-13.32342570057501</v>
       </c>
       <c r="F71">
-        <v>-2.761260166921712</v>
+        <v>2.55880439408029</v>
       </c>
       <c r="G71">
-        <v>-16.11274751327233</v>
+        <v>-10.20514682026741</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.80754714669431</v>
       </c>
       <c r="E72">
-        <v>-27.81834088479286</v>
+        <v>-12.95272251735479</v>
       </c>
       <c r="F72">
-        <v>-3.225288391682717</v>
+        <v>2.855041831199837</v>
       </c>
       <c r="G72">
-        <v>-15.15884801366661</v>
+        <v>-10.40888932815789</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.54167858717834</v>
       </c>
       <c r="E73">
-        <v>-27.27903808784123</v>
+        <v>-13.02577750455852</v>
       </c>
       <c r="F73">
-        <v>-3.345626981022207</v>
+        <v>2.971424137823557</v>
       </c>
       <c r="G73">
-        <v>-14.9886914295685</v>
+        <v>-10.60569508766979</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.30815124712819</v>
       </c>
       <c r="E74">
-        <v>-28.95585978133883</v>
+        <v>-13.16645092534179</v>
       </c>
       <c r="F74">
-        <v>-3.086164914749943</v>
+        <v>2.744204615970458</v>
       </c>
       <c r="G74">
-        <v>-14.65555519825327</v>
+        <v>-10.22529524164933</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.11230003278697</v>
       </c>
       <c r="E75">
-        <v>-26.89972945075596</v>
+        <v>-14.05797926832949</v>
       </c>
       <c r="F75">
-        <v>-3.8896920642417</v>
+        <v>2.623276229040175</v>
       </c>
       <c r="G75">
-        <v>-14.44846702116928</v>
+        <v>-10.12607128271948</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.95578453126633</v>
       </c>
       <c r="E76">
-        <v>-27.99944997103466</v>
+        <v>-13.7511317092285</v>
       </c>
       <c r="F76">
-        <v>-3.192074172300068</v>
+        <v>2.70696950121462</v>
       </c>
       <c r="G76">
-        <v>-15.67323257747529</v>
+        <v>-10.58759087930271</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.83765938514076</v>
       </c>
       <c r="E77">
-        <v>-28.06160693172205</v>
+        <v>-13.90674007793586</v>
       </c>
       <c r="F77">
-        <v>-3.277496247244156</v>
+        <v>2.234346136282168</v>
       </c>
       <c r="G77">
-        <v>-16.2960165620793</v>
+        <v>-10.75651388658152</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.75691777815096</v>
       </c>
       <c r="E78">
-        <v>-26.92078207896152</v>
+        <v>-14.08347167944128</v>
       </c>
       <c r="F78">
-        <v>-3.411837559160569</v>
+        <v>2.696386279276454</v>
       </c>
       <c r="G78">
-        <v>-15.37916352822148</v>
+        <v>-10.19035825753105</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.70419788499937</v>
       </c>
       <c r="E79">
-        <v>-27.81847794076658</v>
+        <v>-14.19074082153896</v>
       </c>
       <c r="F79">
-        <v>-3.130630848564818</v>
+        <v>2.36232558654508</v>
       </c>
       <c r="G79">
-        <v>-15.44286178012775</v>
+        <v>-10.66972882025602</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.6753966134148</v>
       </c>
       <c r="E80">
-        <v>-27.56788978227173</v>
+        <v>-14.27742664831078</v>
       </c>
       <c r="F80">
-        <v>-3.199337297687814</v>
+        <v>2.691740794881554</v>
       </c>
       <c r="G80">
-        <v>-15.35350251963542</v>
+        <v>-9.961453393271421</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.65692238150373</v>
       </c>
       <c r="E81">
-        <v>-29.17036068663225</v>
+        <v>-15.09454605720284</v>
       </c>
       <c r="F81">
-        <v>-3.678252113044529</v>
+        <v>2.677714878017353</v>
       </c>
       <c r="G81">
-        <v>-14.89798763561175</v>
+        <v>-9.95591600399367</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.64677641447189</v>
       </c>
       <c r="E82">
-        <v>-29.40618002565601</v>
+        <v>-16.44924468034674</v>
       </c>
       <c r="F82">
-        <v>-3.38710085177817</v>
+        <v>2.529370843524017</v>
       </c>
       <c r="G82">
-        <v>-15.2667866380416</v>
+        <v>-9.580523566098968</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.63366697691776</v>
       </c>
       <c r="E83">
-        <v>-29.62064147544185</v>
+        <v>-16.87449614110726</v>
       </c>
       <c r="F83">
-        <v>-3.401746387459665</v>
+        <v>2.388448980959766</v>
       </c>
       <c r="G83">
-        <v>-15.03101943162422</v>
+        <v>-9.632379480539957</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.6190486267464</v>
       </c>
       <c r="E84">
-        <v>-30.55424807896704</v>
+        <v>-17.82400746740089</v>
       </c>
       <c r="F84">
-        <v>-3.201431410482091</v>
+        <v>2.170916387515004</v>
       </c>
       <c r="G84">
-        <v>-15.21764459260307</v>
+        <v>-9.651349150738985</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.59431968018707</v>
       </c>
       <c r="E85">
-        <v>-30.0578417251839</v>
+        <v>-18.91261399417435</v>
       </c>
       <c r="F85">
-        <v>-2.625826238401007</v>
+        <v>2.200694538910841</v>
       </c>
       <c r="G85">
-        <v>-13.75610930395669</v>
+        <v>-9.944910410169832</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.56253634210316</v>
       </c>
       <c r="E86">
-        <v>-30.92575075536729</v>
+        <v>-18.44124527486293</v>
       </c>
       <c r="F86">
-        <v>-3.448685826339299</v>
+        <v>2.183515855711585</v>
       </c>
       <c r="G86">
-        <v>-15.39116251036223</v>
+        <v>-9.766420329336894</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.5154390568885</v>
       </c>
       <c r="E87">
-        <v>-33.37216873717261</v>
+        <v>-21.25751710817254</v>
       </c>
       <c r="F87">
-        <v>-3.200450623477177</v>
+        <v>2.110304744652165</v>
       </c>
       <c r="G87">
-        <v>-15.66858936822</v>
+        <v>-9.388705634128398</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.45609975071677</v>
       </c>
       <c r="E88">
-        <v>-33.41651672769913</v>
+        <v>-21.20850506132824</v>
       </c>
       <c r="F88">
-        <v>-3.73578388590376</v>
+        <v>2.166907089285455</v>
       </c>
       <c r="G88">
-        <v>-14.69594341707779</v>
+        <v>-9.285226161515032</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.37926052329782</v>
       </c>
       <c r="E89">
-        <v>-34.58255780301835</v>
+        <v>-24.03209069978087</v>
       </c>
       <c r="F89">
-        <v>-3.280564520104126</v>
+        <v>1.802591105534232</v>
       </c>
       <c r="G89">
-        <v>-13.94557364967837</v>
+        <v>-9.148707716101127</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.29029298529639</v>
       </c>
       <c r="E90">
-        <v>-35.89114539742834</v>
+        <v>-24.96730667269444</v>
       </c>
       <c r="F90">
-        <v>-3.340699851710355</v>
+        <v>1.956710517559886</v>
       </c>
       <c r="G90">
-        <v>-14.73314000063968</v>
+        <v>-9.451123315812735</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.18788496054302</v>
       </c>
       <c r="E91">
-        <v>-37.93366565449974</v>
+        <v>-26.88770590397058</v>
       </c>
       <c r="F91">
-        <v>-3.412322982458609</v>
+        <v>1.658955511358409</v>
       </c>
       <c r="G91">
-        <v>-15.7277279546979</v>
+        <v>-8.926033393808188</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.07834365953246</v>
       </c>
       <c r="E92">
-        <v>-39.03320966329714</v>
+        <v>-28.42319173947861</v>
       </c>
       <c r="F92">
-        <v>-4.042775188646451</v>
+        <v>1.837137339700583</v>
       </c>
       <c r="G92">
-        <v>-14.49641073484048</v>
+        <v>-9.157898842434141</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.96382849788295</v>
       </c>
       <c r="E93">
-        <v>-37.44858095478808</v>
+        <v>-30.59347723653571</v>
       </c>
       <c r="F93">
-        <v>-3.454139797319331</v>
+        <v>1.424618656780457</v>
       </c>
       <c r="G93">
-        <v>-15.83178179112131</v>
+        <v>-9.055838309506045</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.85007012263841</v>
       </c>
       <c r="E94">
-        <v>-39.98336681395178</v>
+        <v>-32.45699616211267</v>
       </c>
       <c r="F94">
-        <v>-3.76313077897238</v>
+        <v>1.281625875709206</v>
       </c>
       <c r="G94">
-        <v>-15.38047020588933</v>
+        <v>-9.476497142493765</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.74217501183989</v>
       </c>
       <c r="E95">
-        <v>-40.52652586761852</v>
+        <v>-34.87335527695453</v>
       </c>
       <c r="F95">
-        <v>-3.734177681509732</v>
+        <v>1.033828050835762</v>
       </c>
       <c r="G95">
-        <v>-15.43019966886085</v>
+        <v>-9.37808773587634</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.64540996615037</v>
       </c>
       <c r="E96">
-        <v>-43.16177790872981</v>
+        <v>-36.80616638027493</v>
       </c>
       <c r="F96">
-        <v>-3.408549768938857</v>
+        <v>0.6628553066356426</v>
       </c>
       <c r="G96">
-        <v>-16.23895351755134</v>
+        <v>-10.14314033085618</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.56532200171097</v>
       </c>
       <c r="E97">
-        <v>-45.8256995676164</v>
+        <v>-38.83129921813494</v>
       </c>
       <c r="F97">
-        <v>-4.730400484608112</v>
+        <v>0.2988101990251355</v>
       </c>
       <c r="G97">
-        <v>-15.06799410189587</v>
+        <v>-9.750610965465409</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.50619934033639</v>
       </c>
       <c r="E98">
-        <v>-46.43941441357215</v>
+        <v>-42.32608326218745</v>
       </c>
       <c r="F98">
-        <v>-3.766679504925973</v>
+        <v>0.1428534681000726</v>
       </c>
       <c r="G98">
-        <v>-16.35951248127976</v>
+        <v>-10.69522665730513</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.47020726914808</v>
       </c>
       <c r="E99">
-        <v>-49.46383066224254</v>
+        <v>-43.80911819187421</v>
       </c>
       <c r="F99">
-        <v>-4.185067999262336</v>
+        <v>-0.2544199411389311</v>
       </c>
       <c r="G99">
-        <v>-16.40285214686454</v>
+        <v>-10.52977985644939</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.45957556488306</v>
       </c>
       <c r="E100">
-        <v>-49.84014587226543</v>
+        <v>-46.61505372049916</v>
       </c>
       <c r="F100">
-        <v>-4.18471097291173</v>
+        <v>-0.2825339024225435</v>
       </c>
       <c r="G100">
-        <v>-15.65556436345494</v>
+        <v>-11.02275109312177</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.46805136994619</v>
       </c>
       <c r="E101">
-        <v>-50.91072123207215</v>
+        <v>-49.37231257409427</v>
       </c>
       <c r="F101">
-        <v>-3.882195339246364</v>
+        <v>-0.617652420327292</v>
       </c>
       <c r="G101">
-        <v>-16.31297595894317</v>
+        <v>-10.50341264145145</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.50467254181088</v>
       </c>
       <c r="E102">
-        <v>-53.12823289510388</v>
+        <v>-51.79435328202851</v>
       </c>
       <c r="F102">
-        <v>-4.96462053938227</v>
+        <v>-1.005870945486294</v>
       </c>
       <c r="G102">
-        <v>-16.39990853233806</v>
+        <v>-11.3302145675003</v>
       </c>
     </row>
   </sheetData>
